--- a/estimate_forms/046_yoga_instructor_estimate_form--estimate_forms.xlsx
+++ b/estimate_forms/046_yoga_instructor_estimate_form--estimate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -834,8 +834,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,12 +863,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_30,_'label':_'30_minutes'}</t>
+          <t>30_minutes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 30, 'label': '30 minutes'}</t>
+          <t>30 minutes</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_45,_'label':_'45_minutes'}</t>
+          <t>45_minutes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 45, 'label': '45 minutes'}</t>
+          <t>45 minutes</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_60,_'label':_'60_minutes'}</t>
+          <t>60_minutes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 60, 'label': '60 minutes'}</t>
+          <t>60 minutes</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_90,_'label':_'90_minutes'}</t>
+          <t>90_minutes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 90, 'label': '90 minutes'}</t>
+          <t>90 minutes</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'private',_'label':_'private_session'}</t>
+          <t>private_session</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'private', 'label': 'Private Session'}</t>
+          <t>Private Session</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'package',_'label':_'package_(multiple_sessions)'}</t>
+          <t>package_(multiple_sessions)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'package', 'label': 'Package (multiple sessions)'}</t>
+          <t>Package (multiple sessions)</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'group',_'label':_'group_class'}</t>
+          <t>group_class</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'group', 'label': 'Group Class'}</t>
+          <t>Group Class</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'studio',_'label':_'studio'}</t>
+          <t>studio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'studio', 'label': 'Studio'}</t>
+          <t>Studio</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'home',_'label':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'home', 'label': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'online',_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'online', 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'meditation',_'label':_'meditation'}</t>
+          <t>meditation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'meditation', 'label': 'Meditation'}</t>
+          <t>Meditation</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'yoga',_'label':_'yoga'}</t>
+          <t>yoga</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'yoga', 'label': 'Yoga'}</t>
+          <t>Yoga</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'breathwork',_'label':_'breathwork'}</t>
+          <t>breathwork</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'breathwork', 'label': 'Breathwork'}</t>
+          <t>Breathwork</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'4_sessions'}</t>
+          <t>4_sessions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '4 sessions'}</t>
+          <t>4 sessions</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_8,_'label':_'8_sessions'}</t>
+          <t>8_sessions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 8, 'label': '8 sessions'}</t>
+          <t>8 sessions</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_12,_'label':_'12_sessions'}</t>
+          <t>12_sessions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 12, 'label': '12 sessions'}</t>
+          <t>12 sessions</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_120,_'label':_'$120'}</t>
+          <t>$120</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 120, 'label': '$120'}</t>
+          <t>$120</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_180,_'label':_'$180'}</t>
+          <t>$180</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 180, 'label': '$180'}</t>
+          <t>$180</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_240,_'label':_'$240'}</t>
+          <t>$240</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 240, 'label': '$240'}</t>
+          <t>$240</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'1-2',_'label':_'1-2_students'}</t>
+          <t>1-2_students</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': '1-2', 'label': '1-2 students'}</t>
+          <t>1-2 students</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'3-4',_'label':_'3-4_students'}</t>
+          <t>3-4_students</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': '3-4', 'label': '3-4 students'}</t>
+          <t>3-4 students</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'5-10',_'label':_'5-10_students'}</t>
+          <t>5-10_students</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': '5-10', 'label': '5-10 students'}</t>
+          <t>5-10 students</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'11+',_'label':_'more_than_10_students'}</t>
+          <t>more_than_10_students</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': '11+', 'label': 'More than 10 students'}</t>
+          <t>More than 10 students</t>
         </is>
       </c>
     </row>
